--- a/artfynd/A 273-2026 artfynd.xlsx
+++ b/artfynd/A 273-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120447610</v>
+        <v>121654507</v>
       </c>
       <c r="B2" t="n">
-        <v>56849</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V om Vårdalstjärnet, Dls</t>
+          <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329432</v>
+        <v>329470</v>
       </c>
       <c r="R2" t="n">
-        <v>6553476</v>
+        <v>6553267</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,66 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Fågelinventering Klinthögen 2024</t>
-        </is>
-      </c>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120447550</v>
+        <v>121654391</v>
       </c>
       <c r="B3" t="n">
-        <v>56556</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V om Vårdalstjärnet, Dls</t>
+          <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329419</v>
+        <v>329332</v>
       </c>
       <c r="R3" t="n">
-        <v>6553456</v>
+        <v>6553552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lite spillning</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,53 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Fågelinventering Klinthögen 2024</t>
-        </is>
-      </c>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120447520</v>
+        <v>120447396</v>
       </c>
       <c r="B4" t="n">
-        <v>56556</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329498</v>
+        <v>329466</v>
       </c>
       <c r="R4" t="n">
-        <v>6553473</v>
+        <v>6553234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,11 +942,6 @@
           <t>2024-04-12</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hyfsat mkt spillning</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -990,7 +954,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1006,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120447544</v>
+        <v>121654393</v>
       </c>
       <c r="B5" t="n">
-        <v>56593</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,46 +981,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>V om Vårdalstjärnet, Dls</t>
+          <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>329446</v>
+        <v>329470</v>
       </c>
       <c r="R5" t="n">
-        <v>6553186</v>
+        <v>6553371</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,27 +1035,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Inte omöjligt att det var samma som stöttes en stund tidigare.</t>
+          <t>Gammalt boträd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,31 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Fågelinventering Klinthögen 2024</t>
-        </is>
-      </c>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120447569</v>
+        <v>121654395</v>
       </c>
       <c r="B6" t="n">
-        <v>56556</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,39 +1083,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>V om Vårdalstjärnet, Dls</t>
+          <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>329496</v>
+        <v>329530</v>
       </c>
       <c r="R6" t="n">
-        <v>6553477</v>
+        <v>6553311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,17 +1137,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en tallåga, hyfsad hög.</t>
+          <t>Födosökspår gamla</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,26 +1162,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Fågelinventering Klinthögen 2024</t>
-        </is>
-      </c>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120447609</v>
+        <v>121654506</v>
       </c>
       <c r="B7" t="n">
-        <v>56849</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,38 +1185,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>V om Vårdalstjärnet, Dls</t>
+          <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>329441</v>
+        <v>329472</v>
       </c>
       <c r="R7" t="n">
-        <v>6553174</v>
+        <v>6553284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,17 +1239,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>Födosöksspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,66 +1264,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Fågelinventering Klinthögen 2024</t>
-        </is>
-      </c>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654395</v>
+        <v>120447520</v>
       </c>
       <c r="B8" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjällhögen, Dls</t>
+          <t>V om Vårdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>329530</v>
+        <v>329498</v>
       </c>
       <c r="R8" t="n">
-        <v>6553311</v>
+        <v>6553473</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,17 +1341,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökspår gamla</t>
+          <t>Hyfsat mkt spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,65 +1366,73 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121654393</v>
+        <v>120447544</v>
       </c>
       <c r="B9" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjällhögen, Dls</t>
+          <t>V om Vårdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>329470</v>
+        <v>329446</v>
       </c>
       <c r="R9" t="n">
-        <v>6553371</v>
+        <v>6553186</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,17 +1456,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gammalt boträd</t>
+          <t>Inte omöjligt att det var samma som stöttes en stund tidigare.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,15 +1491,1090 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120447550</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>V om Vårdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>329419</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6553456</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lite spillning</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120447569</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>V om Vårdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>329496</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6553477</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en tallåga, hyfsad hög.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120447609</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>V om Vårdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>329441</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6553174</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120447610</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>V om Vårdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>329432</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6553476</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120447643</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>V om Vårdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>329561</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6553437</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Uppflog, såg den inte men bullrigt.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121654500</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bjällhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>329532</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6553452</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Alfred Olofsson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121654503</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bjällhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>329418</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6553289</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121654505</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bjällhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>329420</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6553265</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flera, ca 40 plantor</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121654397</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bjällhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>329530</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6553212</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>4 kvadratmeter</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121654502</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bjällhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>329213</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6553493</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt ca 20m2</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 273-2026 artfynd.xlsx
+++ b/artfynd/A 273-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654507</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654391</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t>Fågelinventering Klinthögen 2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447396</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654393</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654395</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654506</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Fågelinventering Klinthögen 2024</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447520</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
           <t>Fågelinventering Klinthögen 2024</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447544</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
           <t>Fågelinventering Klinthögen 2024</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447550</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Fågelinventering Klinthögen 2024</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447569</t>
         </is>
       </c>
     </row>
@@ -1831,6 +1886,11 @@
           <t>Fågelinventering Klinthögen 2024</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447609</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1940,6 +2000,11 @@
           <t>Fågelinventering Klinthögen 2024</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447610</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,6 +2130,11 @@
           <t>Fågelinventering Klinthögen 2024</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447643</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2167,6 +2237,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654500</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2269,6 +2344,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654503</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2371,6 +2451,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654505</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2473,6 +2558,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654397</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2575,8 +2665,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654502</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>